--- a/fixtures/Demo-Roadmap-Source.xlsx
+++ b/fixtures/Demo-Roadmap-Source.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>API Gateway Migration</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>46387</v>
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Data Pipeline Refactor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>46477</v>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46204</v>
+        <v>46113</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>46568</v>
@@ -534,19 +534,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Search Indexing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46203</v>
+        <v>46477</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -555,16 +555,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pricing Page A/B</t>
+          <t>Logging Pipeline</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46113</v>
+        <v>45931</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>46295</v>
@@ -576,19 +576,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Cache Layer Redesign</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46477</v>
+        <v>46387</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -597,19 +597,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q2 Brand Refresh</t>
+          <t>Service Mesh Adoption</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -618,19 +618,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Annual Conference</t>
+          <t>Database Sharding</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46204</v>
+        <v>46023</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46295</v>
+        <v>46660</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -639,19 +639,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABM Pilot Cohort</t>
+          <t>Onboarding Redesign</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46568</v>
+        <v>46203</v>
       </c>
       <c r="E11" t="n">
         <v>9</v>
@@ -660,19 +660,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>Pricing Page A/B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
@@ -681,12 +681,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vendor Consolidation</t>
+          <t>Self-Serve Trial Flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
@@ -697,6 +697,258 @@
       </c>
       <c r="E13" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Settings Console Refresh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SOC2 Type II Audit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vendor Consolidation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46477</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Office Move</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46477</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Equipment Refresh</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Compliance Training</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Plan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46477</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Incident Response Playbook</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46477</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Security Hardening</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46752</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vendor SLA Renegotiation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E24" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Performance Review Cycle</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E25" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,11 +1070,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>API Gateway Migration</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46081</v>
+        <v>46037</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -831,7 +1083,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Schema lock</t>
+          <t>Canary 10%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -843,11 +1095,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>API Gateway Migration</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46188</v>
+        <v>46162</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -856,7 +1108,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cutover</t>
+          <t>50% traffic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -868,11 +1120,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>API Gateway Migration</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46356</v>
+        <v>46280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -881,12 +1133,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Decommission old</t>
+          <t>100% traffic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -897,7 +1149,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46162</v>
+        <v>46376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -906,32 +1158,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Canary 10%</t>
+          <t>Legacy off</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Data Pipeline Refactor</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46280</v>
+        <v>46081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>100% traffic</t>
+          <t>Schema lock</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -943,11 +1195,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Data Pipeline Refactor</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46446</v>
+        <v>46188</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -956,7 +1208,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Legacy gateway off</t>
+          <t>Cutover</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -968,25 +1220,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mobile SDK 3.0</t>
+          <t>Data Pipeline Refactor</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46275</v>
+        <v>46356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Beta release</t>
+          <t>Decommission old</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -997,16 +1249,16 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46497</v>
+        <v>46275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Beta release</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1018,11 +1270,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Mobile SDK 3.0</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46082</v>
+        <v>46357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1031,7 +1283,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Live to 100%</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1043,20 +1295,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Mobile SDK 3.0</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46157</v>
+        <v>46497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Iteration 2</t>
+          <t>Adoption target met</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1068,11 +1320,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pricing Page A/B</t>
+          <t>Search Indexing</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46239</v>
+        <v>46310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1081,7 +1333,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Winner declared</t>
+          <t>Index built</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1093,20 +1345,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Search Indexing</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46223</v>
+        <v>46417</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1118,20 +1370,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Logging Pipeline</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46366</v>
+        <v>46032</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Public launch</t>
+          <t>Schema design</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1143,11 +1395,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Logging Pipeline</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46446</v>
+        <v>46127</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1156,23 +1408,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Conversion target met</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q2 Brand Refresh</t>
+          <t>Logging Pipeline</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46143</v>
+        <v>46254</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1181,7 +1433,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Site live</t>
+          <t>Volume target met</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1193,20 +1445,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Annual Conference</t>
+          <t>Cache Layer Redesign</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46287</v>
+        <v>46204</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Day 1 keynote</t>
+          <t>Architecture review</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1218,20 +1470,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ABM Pilot Cohort</t>
+          <t>Cache Layer Redesign</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46266</v>
+        <v>46341</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wave 1 launch</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1243,20 +1495,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ABM Pilot Cohort</t>
+          <t>Service Mesh Adoption</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46461</v>
+        <v>46327</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Renewal target</t>
+          <t>POC complete</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1268,20 +1520,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>Service Mesh Adoption</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46113</v>
+        <v>46447</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Evidence collection</t>
+          <t>First service migrated</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1293,11 +1545,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>Service Mesh Adoption</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46341</v>
+        <v>46614</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1306,7 +1558,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Report received</t>
+          <t>50% services</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1318,18 +1570,1063 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Service Mesh Adoption</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46722</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>100% services</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Database Sharding</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Shard key chosen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Database Sharding</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Shard 1 live</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Database Sharding</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46539</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>All shards migrated</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Onboarding Redesign</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mockups</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Onboarding Redesign</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Live to 100%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Onboarding Redesign</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Iteration 2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pricing Page A/B</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Variant launched</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Pricing Page A/B</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Winner declared</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Self-Serve Trial Flow</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Design freeze</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Self-Serve Trial Flow</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Self-Serve Trial Flow</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Public launch</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Self-Serve Trial Flow</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46446</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Conversion target met</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Settings Console Refresh</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Settings Console Refresh</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Phase 2 GA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SOC2 Type II Audit</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Evidence collection</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SOC2 Type II Audit</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Auditor on-site</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SOC2 Type II Audit</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Report received</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Vendor Consolidation</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B43" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Vendor list approved</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Vendor Consolidation</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>First 5 consolidated</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Vendor Consolidation</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Final wave complete</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Equipment Refresh</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PO approved</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Equipment Refresh</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Rollout complete</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46096</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Process designed</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Live in 1 BU</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Org-wide rollout</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Compliance Training</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Curriculum approved</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Compliance Training</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>100% completion</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Plan</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tabletop exercise</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Plan</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Live failover test</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Plan</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46388</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Cert renewal</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Incident Response Playbook</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>v1 draft</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Incident Response Playbook</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>v1 ratified</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Incident Response Playbook</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Drill executed</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Security Hardening</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Baseline scan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Security Hardening</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Phase 1 complete</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Security Hardening</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pentest engaged</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Security Hardening</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Phase 2 complete</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Security Hardening</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>46721</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pentest pass</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Vendor SLA Renegotiation</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Initial terms</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Vendor SLA Renegotiation</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Contracts signed</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Office Move</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>__phantom</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Performance Review Cycle</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>__phantom</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/fixtures/Demo-Roadmap-Source.xlsx
+++ b/fixtures/Demo-Roadmap-Source.xlsx
@@ -450,12 +450,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Auth Service v2</t>
+          <t>Line 3 Automation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
@@ -471,12 +471,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Plant 2 Expansion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
@@ -492,12 +492,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>MES Pipeline Refresh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
@@ -513,12 +513,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mobile SDK 3.0</t>
+          <t>Mobile Operator Console</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
@@ -534,12 +534,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Search Indexing</t>
+          <t>Vision Inspection Rollout</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
@@ -555,12 +555,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Logging Pipeline</t>
+          <t>Sensor Telemetry Rollout</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
@@ -576,12 +576,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cache Layer Redesign</t>
+          <t>Edge Compute Buildout</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
@@ -597,12 +597,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Service Mesh Adoption</t>
+          <t>Robotics Cell Network</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
@@ -618,12 +618,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Sharding</t>
+          <t>Plant Historian Migration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
@@ -639,12 +639,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Compact Series Redesign</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
@@ -660,12 +660,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pricing Page A/B</t>
+          <t>Heavy-Duty Variant Launch</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
@@ -681,12 +681,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Sustainable Materials Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
@@ -702,12 +702,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Settings Console Refresh</t>
+          <t>CAD System Migration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
@@ -723,12 +723,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>ISO 9001 Recertification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C15" s="1" t="n">
@@ -744,12 +744,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vendor Consolidation</t>
+          <t>Supplier Consolidation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
@@ -765,12 +765,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Office Move</t>
+          <t>Warehouse Move</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
@@ -786,12 +786,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Equipment Refresh</t>
+          <t>Fleet Refresh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
@@ -828,12 +828,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Compliance Training</t>
+          <t>Safety Training Refresh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
@@ -849,12 +849,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Disaster Recovery Plan</t>
+          <t>Business Continuity Program</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
@@ -870,12 +870,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Incident Response Playbook</t>
+          <t>Plant Incident Response</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
@@ -891,12 +891,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Security Hardening</t>
+          <t>OT Network Segmentation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C23" s="1" t="n">
@@ -912,12 +912,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vendor SLA Renegotiation</t>
+          <t>3PL Renegotiation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
@@ -933,12 +933,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Performance Review Cycle</t>
+          <t>Inventory Audit Cycle</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="C25" s="1" t="n">
@@ -995,7 +995,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Auth Service v2</t>
+          <t>Line 3 Automation</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Design review</t>
+          <t>Cell design review</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Auth Service v2</t>
+          <t>Line 3 Automation</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Code freeze</t>
+          <t>Equipment delivered</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Auth Service v2</t>
+          <t>Line 3 Automation</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Line live</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1070,7 +1070,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Plant 2 Expansion</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Canary 10%</t>
+          <t>Groundbreaking</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Plant 2 Expansion</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>50% traffic</t>
+          <t>Foundation poured</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Plant 2 Expansion</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>100% traffic</t>
+          <t>Equipment installed</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Gateway Migration</t>
+          <t>Plant 2 Expansion</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Legacy off</t>
+          <t>Commissioning</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>MES Pipeline Refresh</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -1195,7 +1195,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>MES Pipeline Refresh</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cutover</t>
+          <t>MES cutover</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1220,7 +1220,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Pipeline Refactor</t>
+          <t>MES Pipeline Refresh</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Decommission old</t>
+          <t>Legacy SCADA off</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mobile SDK 3.0</t>
+          <t>Mobile Operator Console</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Beta release</t>
+          <t>Pilot floor rollout</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mobile SDK 3.0</t>
+          <t>Mobile Operator Console</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Full deployment</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mobile SDK 3.0</t>
+          <t>Mobile Operator Console</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1320,7 +1320,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Search Indexing</t>
+          <t>Vision Inspection Rollout</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Index built</t>
+          <t>Cameras installed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Search Indexing</t>
+          <t>Vision Inspection Rollout</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Inspection live</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Logging Pipeline</t>
+          <t>Sensor Telemetry Rollout</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Schema design</t>
+          <t>Tag mapping complete</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Logging Pipeline</t>
+          <t>Sensor Telemetry Rollout</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Telemetry live</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1420,7 +1420,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Logging Pipeline</t>
+          <t>Sensor Telemetry Rollout</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Volume target met</t>
+          <t>Coverage target met</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cache Layer Redesign</t>
+          <t>Edge Compute Buildout</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Architecture review</t>
+          <t>Reference architecture</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cache Layer Redesign</t>
+          <t>Edge Compute Buildout</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Edge nodes live</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Service Mesh Adoption</t>
+          <t>Robotics Cell Network</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>POC complete</t>
+          <t>POC cell complete</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Service Mesh Adoption</t>
+          <t>Robotics Cell Network</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>First service migrated</t>
+          <t>First cell migrated</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Service Mesh Adoption</t>
+          <t>Robotics Cell Network</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50% services</t>
+          <t>50% cells migrated</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Service Mesh Adoption</t>
+          <t>Robotics Cell Network</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>100% services</t>
+          <t>All cells migrated</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Sharding</t>
+          <t>Plant Historian Migration</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shard key chosen</t>
+          <t>Plant 1 tag mapping</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Sharding</t>
+          <t>Plant Historian Migration</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shard 1 live</t>
+          <t>Plant 1 cut over</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Sharding</t>
+          <t>Plant Historian Migration</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>All shards migrated</t>
+          <t>All plants migrated</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Compact Series Redesign</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mockups</t>
+          <t>Concept review</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Compact Series Redesign</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Live to 100%</t>
+          <t>Pilot production run</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1720,7 +1720,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Onboarding Redesign</t>
+          <t>Compact Series Redesign</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Iteration 2</t>
+          <t>V2 spec released</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pricing Page A/B</t>
+          <t>Heavy-Duty Variant Launch</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Variant launched</t>
+          <t>Prototype A complete</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1770,7 +1770,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pricing Page A/B</t>
+          <t>Heavy-Duty Variant Launch</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Winner declared</t>
+          <t>Launch approved</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Sustainable Materials Program</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design freeze</t>
+          <t>Material spec frozen</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1820,7 +1820,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Sustainable Materials Program</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>First test batch</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Sustainable Materials Program</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Public launch</t>
+          <t>Customer shipments begin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Self-Serve Trial Flow</t>
+          <t>Sustainable Materials Program</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Conversion target met</t>
+          <t>Adoption target met</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Settings Console Refresh</t>
+          <t>CAD System Migration</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>Engineering pilot</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Settings Console Refresh</t>
+          <t>CAD System Migration</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Phase 2 GA</t>
+          <t>Org-wide rollout</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1945,7 +1945,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>ISO 9001 Recertification</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Evidence collection</t>
+          <t>Internal audit complete</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>ISO 9001 Recertification</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Auditor on-site</t>
+          <t>External auditor on-site</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOC2 Type II Audit</t>
+          <t>ISO 9001 Recertification</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Report received</t>
+          <t>Certificate received</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2020,7 +2020,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Vendor Consolidation</t>
+          <t>Supplier Consolidation</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Vendor list approved</t>
+          <t>Supplier list approved</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vendor Consolidation</t>
+          <t>Supplier Consolidation</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -2070,7 +2070,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vendor Consolidation</t>
+          <t>Supplier Consolidation</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -2095,7 +2095,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Equipment Refresh</t>
+          <t>Fleet Refresh</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -2120,7 +2120,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Equipment Refresh</t>
+          <t>Fleet Refresh</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Rollout complete</t>
+          <t>Fleet replacement complete</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Live in 1 BU</t>
+          <t>Pilot site live</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Compliance Training</t>
+          <t>Safety Training Refresh</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -2245,7 +2245,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Compliance Training</t>
+          <t>Safety Training Refresh</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -2270,7 +2270,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Disaster Recovery Plan</t>
+          <t>Business Continuity Program</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -2295,7 +2295,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Disaster Recovery Plan</t>
+          <t>Business Continuity Program</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Live failover test</t>
+          <t>Plant failover test</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Disaster Recovery Plan</t>
+          <t>Business Continuity Program</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cert renewal</t>
+          <t>Recertification complete</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Incident Response Playbook</t>
+          <t>Plant Incident Response</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -2370,7 +2370,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Incident Response Playbook</t>
+          <t>Plant Incident Response</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -2395,7 +2395,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Incident Response Playbook</t>
+          <t>Plant Incident Response</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Drill executed</t>
+          <t>Cross-plant drill</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2420,7 +2420,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Security Hardening</t>
+          <t>OT Network Segmentation</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -2445,7 +2445,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Security Hardening</t>
+          <t>OT Network Segmentation</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Phase 1 complete</t>
+          <t>Plant 1 segmented</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Security Hardening</t>
+          <t>OT Network Segmentation</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -2495,7 +2495,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Security Hardening</t>
+          <t>OT Network Segmentation</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Phase 2 complete</t>
+          <t>All plants segmented</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2520,7 +2520,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Security Hardening</t>
+          <t>OT Network Segmentation</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -2545,7 +2545,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Vendor SLA Renegotiation</t>
+          <t>3PL Renegotiation</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -2570,7 +2570,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vendor SLA Renegotiation</t>
+          <t>3PL Renegotiation</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -2595,7 +2595,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Office Move</t>
+          <t>Warehouse Move</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2615,7 +2615,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Performance Review Cycle</t>
+          <t>Inventory Audit Cycle</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">

--- a/fixtures/Demo-Roadmap-Source.xlsx
+++ b/fixtures/Demo-Roadmap-Source.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
           <t>SortOrder</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Activity Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,6 +493,11 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Permits cleared; foundation contractor confirmed for May start.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -530,6 +540,11 @@
       <c r="E5" t="n">
         <v>3</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pilot floor adoption running ahead of target — 38 of 40 operators trained.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -614,6 +629,11 @@
       <c r="E9" t="n">
         <v>7</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vendor SLA renegotiation may push final cell migration into Q1 2028.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -698,6 +718,11 @@
       <c r="E13" t="n">
         <v>11</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Material spec frozen after 3 rounds with engineering and procurement.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -740,6 +765,11 @@
       <c r="E15" t="n">
         <v>13</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>External auditor confirmed for Aug 1–4; evidence binders 80% ready.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -824,6 +854,11 @@
       <c r="E19" t="n">
         <v>17</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pilot site (Plant 1) live and stable; org-wide rollout cleared for Nov.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -866,6 +901,11 @@
       <c r="E21" t="n">
         <v>19</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tabletop exercise revealed gap in supplier-escalation path; remediation in v1.1.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -907,6 +947,11 @@
       </c>
       <c r="E23" t="n">
         <v>21</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pentest scope expanded to include the new robotics cell network.</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -962,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,6 +1036,11 @@
           <t>Label Position</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Milestone Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1116,6 +1166,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Concrete pour delayed 3 days due to weather; on critical path.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1141,6 +1196,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Two CNC mills arriving Q3 from Yamazaki; install crew booked.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1216,6 +1276,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cutover plan reviewed with operations; rollback path documented.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1291,6 +1356,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hardware refresh (Zebra TC52) ordered alongside software rollout.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1991,6 +2061,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lead auditor: Mary Chen, KPMG. 4-day on-site engagement.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2016,6 +2091,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Certificate valid through November 2029 (3-year cycle).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2066,6 +2146,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>First 5 consolidated: ~12% spend reduction realized in Q4.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2391,6 +2476,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>v1 ratified by ops council; rollout to all 3 plants begins Q1.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2466,6 +2556,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>VLAN inventory complete; 47 firewall rule changes approved.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2489,6 +2584,11 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>External pentest firm: Praetorian Security; SOW signed.</t>
         </is>
       </c>
     </row>
